--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484038_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484038_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.1413</v>
+        <v>7.3414</v>
       </c>
       <c r="E2" t="n">
-        <v>5.0623</v>
+        <v>5.4308</v>
       </c>
       <c r="F2" t="n">
-        <v>2.079</v>
+        <v>1.9107</v>
       </c>
       <c r="G2" t="n">
         <v>5.905</v>
@@ -610,13 +610,13 @@
         <v>1.5871</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3752</v>
+        <v>0.5753</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1928</v>
+        <v>0.5612</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1824</v>
+        <v>0.0141</v>
       </c>
       <c r="V2" t="n">
         <v>0.266</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.8947</v>
+        <v>4.6384</v>
       </c>
       <c r="E3" t="n">
-        <v>3.7227</v>
+        <v>2.6627</v>
       </c>
       <c r="F3" t="n">
-        <v>2.172</v>
+        <v>1.9757</v>
       </c>
       <c r="G3" t="n">
         <v>3.7074</v>
@@ -688,13 +688,13 @@
         <v>1.7855</v>
       </c>
       <c r="S3" t="n">
-        <v>2.3857</v>
+        <v>1.1294</v>
       </c>
       <c r="T3" t="n">
-        <v>1.2301</v>
+        <v>0.1701</v>
       </c>
       <c r="U3" t="n">
-        <v>1.1556</v>
+        <v>0.9592000000000001</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.294</v>
+        <v>2.79</v>
       </c>
       <c r="E4" t="n">
-        <v>1.8088</v>
+        <v>2.5853</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4852</v>
+        <v>0.2046</v>
       </c>
       <c r="G4" t="n">
         <v>0.1933</v>
@@ -766,13 +766,13 @@
         <v>1.9838</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4137</v>
+        <v>0.9097</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8615</v>
+        <v>-0.0849</v>
       </c>
       <c r="U4" t="n">
-        <v>1.2752</v>
+        <v>0.9946</v>
       </c>
       <c r="V4" t="n">
         <v>2.6789</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2522</v>
+        <v>2.5974</v>
       </c>
       <c r="E5" t="n">
-        <v>1.6362</v>
+        <v>1.9253</v>
       </c>
       <c r="F5" t="n">
-        <v>0.616</v>
+        <v>0.6721</v>
       </c>
       <c r="G5" t="n">
         <v>0.8152</v>
@@ -844,13 +844,13 @@
         <v>0.9919</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4954</v>
+        <v>-0.1502</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4364</v>
+        <v>-0.1474</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.059</v>
+        <v>-0.0029</v>
       </c>
       <c r="V5" t="n">
         <v>0.9405</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. BUSCAIL BRIANSO</t>
+          <t>J. CAMPENY LLOVERAS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.9818</v>
+        <v>2.141</v>
       </c>
       <c r="E6" t="n">
-        <v>1.3577</v>
+        <v>0.0244</v>
       </c>
       <c r="F6" t="n">
-        <v>0.624</v>
+        <v>2.1165</v>
       </c>
       <c r="G6" t="n">
-        <v>2.9814</v>
+        <v>2.7578</v>
       </c>
       <c r="H6" t="n">
-        <v>1.2751</v>
+        <v>0.7057</v>
       </c>
       <c r="I6" t="n">
-        <v>1.7063</v>
+        <v>2.0522</v>
       </c>
       <c r="J6" t="n">
-        <v>3.2111</v>
+        <v>3.0516</v>
       </c>
       <c r="K6" t="n">
-        <v>1.9259</v>
+        <v>1.563</v>
       </c>
       <c r="L6" t="n">
-        <v>1.2852</v>
+        <v>1.4885</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.2298</v>
+        <v>-0.2937</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6509</v>
+        <v>-0.8574000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4211</v>
+        <v>0.5637</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.3968</v>
+        <v>-1.3887</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.9838</v>
+        <v>-2.9758</v>
       </c>
       <c r="R6" t="n">
         <v>1.5871</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6036</v>
+        <v>0.5058</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1304</v>
+        <v>-0.3174</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4732</v>
+        <v>0.8232</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.2065</v>
+        <v>0.266</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.2065</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. FERNANDEZ LINARES</t>
+          <t>M. BUSCAIL BRIANSO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.9206</v>
+        <v>2.1305</v>
       </c>
       <c r="E7" t="n">
-        <v>1.8796</v>
+        <v>1.6468</v>
       </c>
       <c r="F7" t="n">
-        <v>0.041</v>
+        <v>0.4838</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7688</v>
+        <v>2.9814</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.177</v>
+        <v>1.2751</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9458</v>
+        <v>1.7063</v>
       </c>
       <c r="J7" t="n">
-        <v>1.469</v>
+        <v>3.2111</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1411</v>
+        <v>1.9259</v>
       </c>
       <c r="L7" t="n">
-        <v>1.3279</v>
+        <v>1.2852</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.7002</v>
+        <v>-0.2298</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3181</v>
+        <v>-0.6509</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.3821</v>
+        <v>0.4211</v>
       </c>
       <c r="P7" t="n">
-        <v>1.1903</v>
+        <v>-0.3968</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.9838</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1903</v>
+        <v>1.5871</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0385</v>
+        <v>0.7524</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1926</v>
+        <v>0.4195</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1541</v>
+        <v>0.3329</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-1.2065</v>
       </c>
       <c r="W7" t="n">
-        <v>0.6032</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.6032</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. CAMPENY LLOVERAS</t>
+          <t>D. FERNANDEZ LINARES</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.9066</v>
+        <v>1.8514</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.4064</v>
+        <v>1.6982</v>
       </c>
       <c r="F8" t="n">
-        <v>2.3129</v>
+        <v>0.1532</v>
       </c>
       <c r="G8" t="n">
-        <v>2.7578</v>
+        <v>0.7688</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7057</v>
+        <v>-0.177</v>
       </c>
       <c r="I8" t="n">
-        <v>2.0522</v>
+        <v>0.9458</v>
       </c>
       <c r="J8" t="n">
-        <v>3.0516</v>
+        <v>1.469</v>
       </c>
       <c r="K8" t="n">
-        <v>1.563</v>
+        <v>0.1411</v>
       </c>
       <c r="L8" t="n">
-        <v>1.4885</v>
+        <v>1.3279</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2937</v>
+        <v>-0.7002</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8574000000000001</v>
+        <v>-0.3181</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5637</v>
+        <v>-0.3821</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.3887</v>
+        <v>1.1903</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.9758</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5871</v>
+        <v>1.1903</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2714</v>
+        <v>-0.1077</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7481</v>
+        <v>-0.374</v>
       </c>
       <c r="U8" t="n">
-        <v>1.0196</v>
+        <v>0.2663</v>
       </c>
       <c r="V8" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.266</v>
+        <v>0.6032</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.6032</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3674</v>
+        <v>1.4463</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.2743</v>
+        <v>-0.5601</v>
       </c>
       <c r="F9" t="n">
-        <v>1.6417</v>
+        <v>2.0064</v>
       </c>
       <c r="G9" t="n">
         <v>2.649</v>
@@ -1156,13 +1156,13 @@
         <v>1.5871</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2897</v>
+        <v>0.7893</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3004</v>
+        <v>0.4138</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0107</v>
+        <v>0.3754</v>
       </c>
       <c r="V9" t="n">
         <v>-0.6032</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. SENGHOR</t>
+          <t>A. BLÁZQUEZ FARRIOL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1433</v>
+        <v>0.1378</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7566000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8999</v>
+        <v>0.0978</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.1265</v>
+        <v>0.7486</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.6174</v>
+        <v>-0.3177</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5091</v>
+        <v>1.0663</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.0311</v>
+        <v>1.406</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.6321</v>
+        <v>0.0806</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.3991</v>
+        <v>1.3253</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.0954</v>
+        <v>-0.6574</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0147</v>
+        <v>-0.3983</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.11</v>
+        <v>-0.2591</v>
       </c>
       <c r="P10" t="n">
-        <v>0.5952</v>
+        <v>-0.5952</v>
       </c>
       <c r="Q10" t="n">
         <v>-0.9919</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5871</v>
+        <v>0.3968</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4682</v>
+        <v>-0.0156</v>
       </c>
       <c r="T10" t="n">
-        <v>1.06</v>
+        <v>-0.3741</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5918</v>
+        <v>0.3585</v>
       </c>
       <c r="V10" t="n">
-        <v>1.2065</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.2065</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. BLÁZQUEZ FARRIOL</t>
+          <t>A. SENGHOR</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1098</v>
+        <v>-0.0301</v>
       </c>
       <c r="E11" t="n">
-        <v>0.04</v>
+        <v>-1.2667</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0698</v>
+        <v>1.2366</v>
       </c>
       <c r="G11" t="n">
-        <v>0.7486</v>
+        <v>-2.1265</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3177</v>
+        <v>-1.6174</v>
       </c>
       <c r="I11" t="n">
-        <v>1.0663</v>
+        <v>-0.5091</v>
       </c>
       <c r="J11" t="n">
-        <v>1.406</v>
+        <v>-2.0311</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0806</v>
+        <v>-1.6321</v>
       </c>
       <c r="L11" t="n">
-        <v>1.3253</v>
+        <v>-0.3991</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.6574</v>
+        <v>-0.0954</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.3983</v>
+        <v>0.0147</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.2591</v>
+        <v>-0.11</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.5952</v>
+        <v>0.5952</v>
       </c>
       <c r="Q11" t="n">
         <v>-0.9919</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3968</v>
+        <v>1.5871</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0436</v>
+        <v>0.2947</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3741</v>
+        <v>0.5499000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3304</v>
+        <v>-0.2551</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.2065</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.2065</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.2046</v>
+        <v>-0.1205</v>
       </c>
       <c r="E12" t="n">
         <v>-0.6656</v>
       </c>
       <c r="F12" t="n">
-        <v>0.461</v>
+        <v>0.5452</v>
       </c>
       <c r="G12" t="n">
         <v>0.2668</v>
@@ -1390,13 +1390,13 @@
         <v>0.1984</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0561</v>
+        <v>0.1403</v>
       </c>
       <c r="T12" t="n">
         <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0561</v>
+        <v>0.1403</v>
       </c>
       <c r="V12" t="n">
         <v>0.266</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.4729</v>
+        <v>-1.6543</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.4455</v>
+        <v>-0.6269</v>
       </c>
       <c r="F13" t="n">
         <v>-1.0275</v>
@@ -1468,10 +1468,10 @@
         <v>0.3968</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1474</v>
+        <v>-0.034</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2438</v>
+        <v>0.0624</v>
       </c>
       <c r="U13" t="n">
         <v>-0.0964</v>
@@ -1501,19 +1501,19 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>22.3342</v>
+        <v>23.2693</v>
       </c>
       <c r="E14" t="n">
-        <v>11.9589</v>
+        <v>12.8942</v>
       </c>
       <c r="F14" t="n">
-        <v>10.375</v>
+        <v>10.3751</v>
       </c>
       <c r="G14" t="n">
         <v>18.5307</v>
       </c>
       <c r="H14" t="n">
-        <v>1.008200000000001</v>
+        <v>1.0082</v>
       </c>
       <c r="I14" t="n">
         <v>17.5226</v>
@@ -1537,7 +1537,7 @@
         <v>2.8834</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.9838</v>
+        <v>-1.983800000000001</v>
       </c>
       <c r="Q14" t="n">
         <v>-16.8626</v>
@@ -1546,10 +1546,10 @@
         <v>14.879</v>
       </c>
       <c r="S14" t="n">
-        <v>3.8541</v>
+        <v>4.7894</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.05599999999999997</v>
+        <v>0.8791000000000001</v>
       </c>
       <c r="U14" t="n">
         <v>3.9101</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.3902</v>
+        <v>1.7702</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1934</v>
+        <v>0.6015</v>
       </c>
       <c r="F15" t="n">
-        <v>1.1968</v>
+        <v>1.1687</v>
       </c>
       <c r="G15" t="n">
         <v>2.1514</v>
@@ -1624,13 +1624,13 @@
         <v>1.5871</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3645</v>
+        <v>0.0156</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4137</v>
+        <v>-0.0056</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0492</v>
+        <v>0.0212</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.543</v>
+        <v>-0.059</v>
       </c>
       <c r="E16" t="n">
-        <v>1.1327</v>
+        <v>0.4185</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.5898</v>
+        <v>-0.4776</v>
       </c>
       <c r="G16" t="n">
         <v>-1.8546</v>
@@ -1702,13 +1702,13 @@
         <v>2.1822</v>
       </c>
       <c r="S16" t="n">
-        <v>0.7267</v>
+        <v>0.1247</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3856</v>
+        <v>-0.3286</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3411</v>
+        <v>0.4534</v>
       </c>
       <c r="V16" t="n">
         <v>1.4724</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.44</v>
+        <v>-0.4119</v>
       </c>
       <c r="E17" t="n">
         <v>0.4134</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.8532999999999999</v>
+        <v>-0.8253</v>
       </c>
       <c r="G17" t="n">
         <v>-0.2716</v>
@@ -1780,13 +1780,13 @@
         <v>0.1984</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3667</v>
+        <v>-0.3387</v>
       </c>
       <c r="T17" t="n">
         <v>-0.2494</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1173</v>
+        <v>-0.0893</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. MORENO MARTIN</t>
+          <t>J. SERRA ANGLÈS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.8639</v>
+        <v>-0.5807</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6273</v>
+        <v>0.6768</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.4912</v>
+        <v>-1.2575</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.1953</v>
+        <v>-1.2097</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.0658</v>
+        <v>1.3555</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1295</v>
+        <v>-2.5652</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0605</v>
+        <v>-0.1784</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0605</v>
+        <v>1.059</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>-1.2374</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.2558</v>
+        <v>-1.0314</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1263</v>
+        <v>0.2965</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1295</v>
+        <v>-1.3279</v>
       </c>
       <c r="P18" t="n">
-        <v>0.1984</v>
+        <v>2.3806</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.1984</v>
+        <v>2.3806</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3395</v>
+        <v>-0.2792</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5669</v>
+        <v>-0.3513</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2273</v>
+        <v>0.0722</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.2065</v>
+        <v>-1.4724</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.2065</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2065</v>
+        <v>-2.6789</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>O. JIMENEZ ROCA</t>
+          <t>A. BELTRAN MATA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.1955</v>
+        <v>-0.9312</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1247</v>
+        <v>0.8796</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.0708</v>
+        <v>-1.8107</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.6688</v>
+        <v>-0.0709</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.4032</v>
+        <v>-0.0955</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2656</v>
+        <v>0.0246</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>2.7783</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>0.8881</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.8901</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.6688</v>
+        <v>-2.8492</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4032</v>
+        <v>-0.9837</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.2656</v>
+        <v>-1.8655</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.3887</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.3806</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2607</v>
+        <v>-0.7765</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1247</v>
+        <v>-0.9068000000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.136</v>
+        <v>0.1303</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.266</v>
+        <v>-1.4724</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.266</v>
+        <v>-1.4724</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. BELTRAN MATA</t>
+          <t>P. MORENO MARTIN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.3835</v>
+        <v>-0.9838</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6755</v>
+        <v>0.4233</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.059</v>
+        <v>-1.407</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.0709</v>
+        <v>-0.1953</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.0955</v>
+        <v>-0.0658</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0246</v>
+        <v>-0.1295</v>
       </c>
       <c r="J20" t="n">
-        <v>2.7783</v>
+        <v>0.0605</v>
       </c>
       <c r="K20" t="n">
-        <v>0.8881</v>
+        <v>0.0605</v>
       </c>
       <c r="L20" t="n">
-        <v>1.8901</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.8492</v>
+        <v>-0.2558</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.9837</v>
+        <v>-0.1263</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.8655</v>
+        <v>-0.1295</v>
       </c>
       <c r="P20" t="n">
-        <v>1.3887</v>
+        <v>0.1984</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.3806</v>
+        <v>0.1984</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.2288</v>
+        <v>0.2196</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.1109</v>
+        <v>0.3628</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.118</v>
+        <v>-0.1432</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.4724</v>
+        <v>-1.2065</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.4724</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. SERRA ANGLÈS</t>
+          <t>O. JIMENEZ ROCA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.5117</v>
+        <v>-1.1955</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1666</v>
+        <v>-0.1247</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.6783</v>
+        <v>-1.0708</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.2097</v>
+        <v>-0.6688</v>
       </c>
       <c r="H21" t="n">
-        <v>1.3555</v>
+        <v>-0.4032</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.5652</v>
+        <v>-0.2656</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.1784</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>1.059</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.2374</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.0314</v>
+        <v>-0.6688</v>
       </c>
       <c r="N21" t="n">
-        <v>0.2965</v>
+        <v>-0.4032</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.3279</v>
+        <v>-0.2656</v>
       </c>
       <c r="P21" t="n">
-        <v>2.3806</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.3806</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.2101</v>
+        <v>-0.2607</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8615</v>
+        <v>-0.1247</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3486</v>
+        <v>-0.136</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.4724</v>
+        <v>-0.266</v>
       </c>
       <c r="W21" t="n">
-        <v>1.2065</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.6789</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.6149</v>
+        <v>-2.6088</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.1128</v>
+        <v>-4.3168</v>
       </c>
       <c r="F22" t="n">
-        <v>2.4978</v>
+        <v>1.7081</v>
       </c>
       <c r="G22" t="n">
         <v>-2.0883</v>
@@ -2170,13 +2170,13 @@
         <v>1.9838</v>
       </c>
       <c r="S22" t="n">
-        <v>1.1794</v>
+        <v>0.1856</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.493</v>
+        <v>-0.6971000000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>1.6725</v>
+        <v>0.8827</v>
       </c>
       <c r="V22" t="n">
         <v>1.2777</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.2993</v>
+        <v>-3.3571</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.7402</v>
+        <v>-1.0463</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.5591</v>
+        <v>-2.3108</v>
       </c>
       <c r="G23" t="n">
         <v>-2.6964</v>
@@ -2248,13 +2248,13 @@
         <v>1.3887</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.611</v>
+        <v>-0.6688</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0679</v>
+        <v>-0.374</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.543</v>
+        <v>-0.2948</v>
       </c>
       <c r="V23" t="n">
         <v>0.6032</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.3389</v>
+        <v>-4.5422</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.3884</v>
+        <v>-2.9803</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.9505</v>
+        <v>-1.562</v>
       </c>
       <c r="G24" t="n">
         <v>-4.9032</v>
@@ -2326,13 +2326,13 @@
         <v>2.579</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.6341</v>
+        <v>-0.8374</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.3602</v>
+        <v>-0.9520999999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2738</v>
+        <v>0.1147</v>
       </c>
       <c r="V24" t="n">
         <v>0.6032</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-8.6196</v>
+        <v>-8.754</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.2181</v>
+        <v>-5.3201</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.4016</v>
+        <v>-3.4339</v>
       </c>
       <c r="G25" t="n">
         <v>-6.7232</v>
@@ -2404,13 +2404,13 @@
         <v>1.9838</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.4239</v>
+        <v>-0.5583</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.1813</v>
+        <v>-0.2833</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.2427</v>
+        <v>-0.275</v>
       </c>
       <c r="V25" t="n">
         <v>-1.4724</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-22.3341</v>
+        <v>-21.654</v>
       </c>
       <c r="E26" t="n">
-        <v>-10.3753</v>
+        <v>-10.3751</v>
       </c>
       <c r="F26" t="n">
-        <v>-11.959</v>
+        <v>-11.2788</v>
       </c>
       <c r="G26" t="n">
         <v>-18.5306</v>
@@ -2482,13 +2482,13 @@
         <v>16.8626</v>
       </c>
       <c r="S26" t="n">
-        <v>-3.8542</v>
+        <v>-3.1741</v>
       </c>
       <c r="T26" t="n">
-        <v>-3.910099999999999</v>
+        <v>-3.9101</v>
       </c>
       <c r="U26" t="n">
-        <v>0.05610000000000012</v>
+        <v>0.7362000000000001</v>
       </c>
       <c r="V26" t="n">
         <v>-1.9332</v>
